--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260916.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260916.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>6,378,000</t>
+          <t>6,445,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.97%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.93%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.36%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>37,056,000</t>
+          <t>37,372,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -704,46 +704,46 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>50,995,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,331,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,171 +755,171 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>10,592,000</t>
+          <t>12,651,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>21,845,000</t>
+          <t>10,592,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>11,980,000</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>27,131,000</t>
+          <t>4,005,472,521</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>35,990,000</t>
+          <t>27,284,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>36,182,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>3,756,195,604</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.46%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>4,101,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>33,103,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,22 +953,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -985,78 +985,78 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,933,000</t>
+          <t>10,091,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.31%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>2,322,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,322,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>4,364,000</t>
+          <t>4,409,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>4,784,400</t>
+          <t>18,807,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>18,807,000</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1232,24 +1232,24 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,562,601,204</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,39 +1261,39 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>2,599,231,204</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>17,775,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,88 +1305,88 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,795,000</t>
+          <t>17,775,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>10,015,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>9,757,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>26,620,004</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1408,29 +1408,29 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>26,620,004</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1452,24 +1452,24 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,61 +1481,61 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1672,73 +1672,73 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>19,286,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>6,733,000</t>
+          <t>20,037,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>16,823,000</t>
+          <t>6,733,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-60,583,107</t>
+          <t>-75,520,278</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
     </row>
